--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/42.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/42.xlsx
@@ -426,13 +426,13 @@
         <v>-7.577755655606969</v>
       </c>
       <c r="E2">
-        <v>-3.965487138796365</v>
+        <v>-8.062633054184136</v>
       </c>
       <c r="F2">
-        <v>-2.60849927743665</v>
+        <v>-3.159349518052474</v>
       </c>
       <c r="G2">
-        <v>-3.277014174172243</v>
+        <v>-2.907520875988647</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.904683142447294</v>
       </c>
       <c r="E3">
-        <v>-4.852103479336122</v>
+        <v>-8.737846642623817</v>
       </c>
       <c r="F3">
-        <v>-2.817266087024987</v>
+        <v>-3.144746229108521</v>
       </c>
       <c r="G3">
-        <v>-2.650337835224825</v>
+        <v>-2.948743789043652</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.213047356439248</v>
       </c>
       <c r="E4">
-        <v>-6.507840373812619</v>
+        <v>-9.540414505581213</v>
       </c>
       <c r="F4">
-        <v>-2.684256789892276</v>
+        <v>-3.236675130001599</v>
       </c>
       <c r="G4">
-        <v>-2.204493425269017</v>
+        <v>-2.678937638138589</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.602503769066469</v>
       </c>
       <c r="E5">
-        <v>-6.99323844574679</v>
+        <v>-9.664032789042597</v>
       </c>
       <c r="F5">
-        <v>-2.650543064965739</v>
+        <v>-3.516935016655951</v>
       </c>
       <c r="G5">
-        <v>-2.480059925412412</v>
+        <v>-2.58099845890479</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.060511462505028</v>
       </c>
       <c r="E6">
-        <v>-7.713292983810422</v>
+        <v>-11.21926925986687</v>
       </c>
       <c r="F6">
-        <v>-2.81679060413578</v>
+        <v>-3.40466555418713</v>
       </c>
       <c r="G6">
-        <v>-1.455638092649257</v>
+        <v>-2.699059133926279</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.611333919819272</v>
       </c>
       <c r="E7">
-        <v>-8.671495441463431</v>
+        <v>-11.52903952436156</v>
       </c>
       <c r="F7">
-        <v>-2.82915315925516</v>
+        <v>-3.822831217692141</v>
       </c>
       <c r="G7">
-        <v>-1.407456412870704</v>
+        <v>-2.14910799839701</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.254202774870521</v>
       </c>
       <c r="E8">
-        <v>-9.808323556348999</v>
+        <v>-12.00427117214851</v>
       </c>
       <c r="F8">
-        <v>-2.998700085790551</v>
+        <v>-3.690768744500829</v>
       </c>
       <c r="G8">
-        <v>-1.1511937037668</v>
+        <v>-1.697708493026306</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.989569103550799</v>
       </c>
       <c r="E9">
-        <v>-10.60396738254866</v>
+        <v>-12.56780806308503</v>
       </c>
       <c r="F9">
-        <v>-2.84300097712776</v>
+        <v>-3.455258921680513</v>
       </c>
       <c r="G9">
-        <v>-0.8686883001730934</v>
+        <v>-1.548849812852977</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.810453713979626</v>
       </c>
       <c r="E10">
-        <v>-10.93756194879771</v>
+        <v>-13.09915203230102</v>
       </c>
       <c r="F10">
-        <v>-3.109890185533524</v>
+        <v>-3.871805955280453</v>
       </c>
       <c r="G10">
-        <v>-0.2136008594076502</v>
+        <v>-1.397293038065142</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.699526227564966</v>
       </c>
       <c r="E11">
-        <v>-10.90424596552328</v>
+        <v>-14.04510949623729</v>
       </c>
       <c r="F11">
-        <v>-2.851225008702753</v>
+        <v>-3.596614848763832</v>
       </c>
       <c r="G11">
-        <v>0.4784090957572846</v>
+        <v>-0.6020106148026422</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.646676593559381</v>
       </c>
       <c r="E12">
-        <v>-12.47853825497182</v>
+        <v>-14.71287827340836</v>
       </c>
       <c r="F12">
-        <v>-2.980091640454063</v>
+        <v>-3.730937936597383</v>
       </c>
       <c r="G12">
-        <v>0.6069575790471848</v>
+        <v>-0.1055181686415245</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.626460455025414</v>
       </c>
       <c r="E13">
-        <v>-13.10809576846617</v>
+        <v>-15.34873489424738</v>
       </c>
       <c r="F13">
-        <v>-2.89684568667713</v>
+        <v>-3.501731161344968</v>
       </c>
       <c r="G13">
-        <v>0.9057442456030272</v>
+        <v>0.3220023717544174</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.62729371294302</v>
       </c>
       <c r="E14">
-        <v>-14.65739993834039</v>
+        <v>-15.98181103204569</v>
       </c>
       <c r="F14">
-        <v>-3.053355767027263</v>
+        <v>-3.494075389808295</v>
       </c>
       <c r="G14">
-        <v>1.32058539658356</v>
+        <v>0.738740465328953</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.628338279469934</v>
       </c>
       <c r="E15">
-        <v>-15.03474862045155</v>
+        <v>-16.0409166747938</v>
       </c>
       <c r="F15">
-        <v>-2.774226601877733</v>
+        <v>-3.297448304507985</v>
       </c>
       <c r="G15">
-        <v>2.368181048121613</v>
+        <v>0.9068896943596151</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.620875325839804</v>
       </c>
       <c r="E16">
-        <v>-15.9474580282235</v>
+        <v>-18.18930172809075</v>
       </c>
       <c r="F16">
-        <v>-2.819902780468098</v>
+        <v>-3.244231497449936</v>
       </c>
       <c r="G16">
-        <v>2.574335339943109</v>
+        <v>1.742739542660344</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.59974912053722</v>
       </c>
       <c r="E17">
-        <v>-16.06366772820834</v>
+        <v>-19.20457654366243</v>
       </c>
       <c r="F17">
-        <v>-2.276485480557594</v>
+        <v>-3.031838923739546</v>
       </c>
       <c r="G17">
-        <v>2.890995641865477</v>
+        <v>1.354362892720744</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.566616799542674</v>
       </c>
       <c r="E18">
-        <v>-17.74557467397516</v>
+        <v>-19.11844043956253</v>
       </c>
       <c r="F18">
-        <v>-2.011885051285765</v>
+        <v>-2.780059136760844</v>
       </c>
       <c r="G18">
-        <v>3.70210909389677</v>
+        <v>1.76587694543431</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.534555590191237</v>
       </c>
       <c r="E19">
-        <v>-18.64511527933281</v>
+        <v>-20.30640861141672</v>
       </c>
       <c r="F19">
-        <v>-1.50954400577788</v>
+        <v>-2.051018784128819</v>
       </c>
       <c r="G19">
-        <v>3.818315863416268</v>
+        <v>2.835798916089208</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.51382639055976</v>
       </c>
       <c r="E20">
-        <v>-19.02359155147188</v>
+        <v>-21.0091960780891</v>
       </c>
       <c r="F20">
-        <v>-1.528612195022922</v>
+        <v>-1.960872529886566</v>
       </c>
       <c r="G20">
-        <v>3.622897670778629</v>
+        <v>2.109855869146744</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.5273282779361</v>
       </c>
       <c r="E21">
-        <v>-20.55040731942401</v>
+        <v>-21.61267410977328</v>
       </c>
       <c r="F21">
-        <v>-1.031859316014323</v>
+        <v>-1.641755585101696</v>
       </c>
       <c r="G21">
-        <v>3.84396928080008</v>
+        <v>1.939597822607565</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.583448128659686</v>
       </c>
       <c r="E22">
-        <v>-20.46089297371439</v>
+        <v>-21.49966604091187</v>
       </c>
       <c r="F22">
-        <v>-0.304565990234802</v>
+        <v>-1.097083308575951</v>
       </c>
       <c r="G22">
-        <v>3.270764873402971</v>
+        <v>1.767264064015265</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.697777741262869</v>
       </c>
       <c r="E23">
-        <v>-19.95291593037797</v>
+        <v>-22.92441906167912</v>
       </c>
       <c r="F23">
-        <v>-0.2110971543399198</v>
+        <v>-0.8646682663724933</v>
       </c>
       <c r="G23">
-        <v>3.126004648607259</v>
+        <v>1.892184189394124</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.869133646743729</v>
       </c>
       <c r="E24">
-        <v>-21.06458384367692</v>
+        <v>-22.77075888165085</v>
       </c>
       <c r="F24">
-        <v>-0.06202415653212073</v>
+        <v>-0.6613521142945771</v>
       </c>
       <c r="G24">
-        <v>2.423132793527976</v>
+        <v>1.035792406022217</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.0947384727927</v>
       </c>
       <c r="E25">
-        <v>-22.10634570371947</v>
+        <v>-23.45675023822879</v>
       </c>
       <c r="F25">
-        <v>0.2050108445365363</v>
+        <v>-0.721744239795675</v>
       </c>
       <c r="G25">
-        <v>2.639374317607631</v>
+        <v>0.7342215706678478</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.359819734966347</v>
       </c>
       <c r="E26">
-        <v>-21.36542395742849</v>
+        <v>-23.30138735197363</v>
       </c>
       <c r="F26">
-        <v>0.152846064080043</v>
+        <v>-0.4789746050572239</v>
       </c>
       <c r="G26">
-        <v>2.093710338551718</v>
+        <v>0.8390301318956342</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.642794575878919</v>
       </c>
       <c r="E27">
-        <v>-21.56284731026688</v>
+        <v>-24.01410123367083</v>
       </c>
       <c r="F27">
-        <v>0.5338379120170225</v>
+        <v>-0.4186412936417247</v>
       </c>
       <c r="G27">
-        <v>1.279004944610314</v>
+        <v>0.3075849459308914</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.920592536893632</v>
       </c>
       <c r="E28">
-        <v>-21.6961655850527</v>
+        <v>-22.19173913808211</v>
       </c>
       <c r="F28">
-        <v>0.5318299494326364</v>
+        <v>-0.08052988431066169</v>
       </c>
       <c r="G28">
-        <v>0.7761032822851676</v>
+        <v>-0.2888429384242057</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.162977907795792</v>
       </c>
       <c r="E29">
-        <v>-21.60752070635255</v>
+        <v>-22.19016322912744</v>
       </c>
       <c r="F29">
-        <v>0.5701030085441819</v>
+        <v>-0.2819499034035699</v>
       </c>
       <c r="G29">
-        <v>0.8382488431483662</v>
+        <v>-0.8680394332473963</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.347128764232596</v>
       </c>
       <c r="E30">
-        <v>-20.97425437264592</v>
+        <v>-22.92264842834212</v>
       </c>
       <c r="F30">
-        <v>0.8391202928077383</v>
+        <v>-0.3317488665576678</v>
       </c>
       <c r="G30">
-        <v>-0.2724822223691275</v>
+        <v>-0.6020304780758778</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.444410176612105</v>
       </c>
       <c r="E31">
-        <v>-20.80368487067301</v>
+        <v>-22.08912391706829</v>
       </c>
       <c r="F31">
-        <v>0.7643385971526101</v>
+        <v>-0.02468963768794702</v>
       </c>
       <c r="G31">
-        <v>0.04313856825390892</v>
+        <v>-1.27047928063782</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.441049664807615</v>
       </c>
       <c r="E32">
-        <v>-20.24060988408527</v>
+        <v>-22.18764992605318</v>
       </c>
       <c r="F32">
-        <v>0.5148326786945934</v>
+        <v>-0.5253673214510102</v>
       </c>
       <c r="G32">
-        <v>-0.3470357079135146</v>
+        <v>-1.156020479163058</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.325064048448036</v>
       </c>
       <c r="E33">
-        <v>-20.09815314875198</v>
+        <v>-22.28863036795022</v>
       </c>
       <c r="F33">
-        <v>0.2934895951969543</v>
+        <v>-0.3679261561401306</v>
       </c>
       <c r="G33">
-        <v>-0.2664967560341252</v>
+        <v>-1.511016898430185</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.099137691316035</v>
       </c>
       <c r="E34">
-        <v>-20.01477941379676</v>
+        <v>-21.73264697165849</v>
       </c>
       <c r="F34">
-        <v>0.2570165784516921</v>
+        <v>-0.4064982558840867</v>
       </c>
       <c r="G34">
-        <v>0.1790794997330017</v>
+        <v>-1.771431031640336</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.773645811647656</v>
       </c>
       <c r="E35">
-        <v>-19.35275727014142</v>
+        <v>-21.63360018816272</v>
       </c>
       <c r="F35">
-        <v>0.483070587369052</v>
+        <v>-0.5911877385426533</v>
       </c>
       <c r="G35">
-        <v>-0.5014229991374265</v>
+        <v>-1.442690549045167</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.36783096316237</v>
       </c>
       <c r="E36">
-        <v>-19.08528295287837</v>
+        <v>-20.86491889620473</v>
       </c>
       <c r="F36">
-        <v>0.1861961357167511</v>
+        <v>-0.8915926920656856</v>
       </c>
       <c r="G36">
-        <v>-0.1425731048625868</v>
+        <v>-1.479596510716963</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.910931461419111</v>
       </c>
       <c r="E37">
-        <v>-17.83966730690654</v>
+        <v>-20.31775696727994</v>
       </c>
       <c r="F37">
-        <v>-0.006296567876186794</v>
+        <v>-0.8540784174951044</v>
       </c>
       <c r="G37">
-        <v>0.128971082450593</v>
+        <v>-0.9710834737027512</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.432812011516343</v>
       </c>
       <c r="E38">
-        <v>-18.68183667506101</v>
+        <v>-19.71539746867566</v>
       </c>
       <c r="F38">
-        <v>-0.1270866174502023</v>
+        <v>-0.6024974386930749</v>
       </c>
       <c r="G38">
-        <v>-0.3051374435684985</v>
+        <v>-0.8949872739370637</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.972748855061834</v>
       </c>
       <c r="E39">
-        <v>-17.43835394034679</v>
+        <v>-19.56895567621562</v>
       </c>
       <c r="F39">
-        <v>-0.2447007064018845</v>
+        <v>-1.099864137947149</v>
       </c>
       <c r="G39">
-        <v>1.049822498017648</v>
+        <v>-0.1537230222388522</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.558292684302135</v>
       </c>
       <c r="E40">
-        <v>-16.06599536384828</v>
+        <v>-18.40207660781515</v>
       </c>
       <c r="F40">
-        <v>-0.1731860917833976</v>
+        <v>-0.9926932768425597</v>
       </c>
       <c r="G40">
-        <v>0.868374807555734</v>
+        <v>0.06499810044971657</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.221884088290883</v>
       </c>
       <c r="E41">
-        <v>-16.96364306707072</v>
+        <v>-18.11605818949069</v>
       </c>
       <c r="F41">
-        <v>-0.2879274025821711</v>
+        <v>-1.23136746314157</v>
       </c>
       <c r="G41">
-        <v>1.128358569845779</v>
+        <v>-0.1358626290544842</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.977711002302205</v>
       </c>
       <c r="E42">
-        <v>-15.99295560657857</v>
+        <v>-18.86120953050483</v>
       </c>
       <c r="F42">
-        <v>-0.5556184706338454</v>
+        <v>-1.488126566578499</v>
       </c>
       <c r="G42">
-        <v>1.693938790865947</v>
+        <v>0.5167452131020449</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.837605992897525</v>
       </c>
       <c r="E43">
-        <v>-15.27100363790572</v>
+        <v>-17.1726230855767</v>
       </c>
       <c r="F43">
-        <v>-0.7327664964573253</v>
+        <v>-1.436030540616438</v>
       </c>
       <c r="G43">
-        <v>1.126352379248981</v>
+        <v>0.6561920123072259</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.79992411368298</v>
       </c>
       <c r="E44">
-        <v>-15.9256715397726</v>
+        <v>-16.97038596486814</v>
       </c>
       <c r="F44">
-        <v>-0.4673319012108769</v>
+        <v>-1.417901720006171</v>
       </c>
       <c r="G44">
-        <v>1.867600078219496</v>
+        <v>1.260773770325548</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.856397254469081</v>
       </c>
       <c r="E45">
-        <v>-13.6784253704142</v>
+        <v>-15.81044451864743</v>
       </c>
       <c r="F45">
-        <v>-0.7829547922907388</v>
+        <v>-1.356679570367468</v>
       </c>
       <c r="G45">
-        <v>1.606844958818801</v>
+        <v>0.9640065365486609</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.995137864376264</v>
       </c>
       <c r="E46">
-        <v>-13.89142667383898</v>
+        <v>-15.81148153919519</v>
       </c>
       <c r="F46">
-        <v>-0.9857730955595726</v>
+        <v>-1.658148147635695</v>
       </c>
       <c r="G46">
-        <v>1.64023512112789</v>
+        <v>0.6027995338498602</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.194056392293556</v>
       </c>
       <c r="E47">
-        <v>-13.16362844522223</v>
+        <v>-15.4354144152282</v>
       </c>
       <c r="F47">
-        <v>-0.7380796449788812</v>
+        <v>-1.641801973676252</v>
       </c>
       <c r="G47">
-        <v>1.988332363491177</v>
+        <v>0.7002785472537003</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.438839975235005</v>
       </c>
       <c r="E48">
-        <v>-12.12396326864524</v>
+        <v>-15.11940844202495</v>
       </c>
       <c r="F48">
-        <v>-1.047463272780857</v>
+        <v>-1.582558793762837</v>
       </c>
       <c r="G48">
-        <v>2.07371464349452</v>
+        <v>0.699139719588191</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.706004067230079</v>
       </c>
       <c r="E49">
-        <v>-12.508752233551</v>
+        <v>-14.43599378715737</v>
       </c>
       <c r="F49">
-        <v>-1.121832441469391</v>
+        <v>-1.846055837654138</v>
       </c>
       <c r="G49">
-        <v>1.748493270807597</v>
+        <v>1.29337602279629</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.987826832911273</v>
       </c>
       <c r="E50">
-        <v>-11.46458575381038</v>
+        <v>-13.89170291075345</v>
       </c>
       <c r="F50">
-        <v>-1.109233801640214</v>
+        <v>-1.928064210531289</v>
       </c>
       <c r="G50">
-        <v>1.62774443280822</v>
+        <v>0.9259749893935134</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.270993052052442</v>
       </c>
       <c r="E51">
-        <v>-11.09158440674659</v>
+        <v>-13.6355633639316</v>
       </c>
       <c r="F51">
-        <v>-1.041591804629814</v>
+        <v>-1.678417469614796</v>
       </c>
       <c r="G51">
-        <v>2.332721794850479</v>
+        <v>0.5330959975205053</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.55471911155424</v>
       </c>
       <c r="E52">
-        <v>-10.74848457355545</v>
+        <v>-13.20796220575733</v>
       </c>
       <c r="F52">
-        <v>-1.25529071373442</v>
+        <v>-2.098293711806587</v>
       </c>
       <c r="G52">
-        <v>1.15138341407141</v>
+        <v>0.3811618205411935</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.836349982588361</v>
       </c>
       <c r="E53">
-        <v>-10.37039322170703</v>
+        <v>-12.69362718491414</v>
       </c>
       <c r="F53">
-        <v>-1.212623993918426</v>
+        <v>-1.839237545561695</v>
       </c>
       <c r="G53">
-        <v>1.313689530225258</v>
+        <v>0.2907739956824723</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.116532666535014</v>
       </c>
       <c r="E54">
-        <v>-9.161838607013978</v>
+        <v>-11.76909845998217</v>
       </c>
       <c r="F54">
-        <v>-1.521913187836483</v>
+        <v>-1.887133748791562</v>
       </c>
       <c r="G54">
-        <v>0.9481854394164838</v>
+        <v>-0.1871032529113236</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.397661558293589</v>
       </c>
       <c r="E55">
-        <v>-10.02486159797377</v>
+        <v>-11.33852209438486</v>
       </c>
       <c r="F55">
-        <v>-1.328815776039501</v>
+        <v>-1.908812123722825</v>
       </c>
       <c r="G55">
-        <v>0.8754726171919315</v>
+        <v>-0.2131307619410737</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.678160791100027</v>
       </c>
       <c r="E56">
-        <v>-8.220971147862331</v>
+        <v>-11.23491966603738</v>
       </c>
       <c r="F56">
-        <v>-1.33602340081126</v>
+        <v>-1.997037393957987</v>
       </c>
       <c r="G56">
-        <v>0.9313579364403685</v>
+        <v>-0.1142447666830433</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.963417879991314</v>
       </c>
       <c r="E57">
-        <v>-7.940269158022875</v>
+        <v>-10.99342067568232</v>
       </c>
       <c r="F57">
-        <v>-1.435691738348693</v>
+        <v>-2.233455107451771</v>
       </c>
       <c r="G57">
-        <v>0.1103658165198889</v>
+        <v>-0.6050828010630859</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.245146071199193</v>
       </c>
       <c r="E58">
-        <v>-7.650727586920448</v>
+        <v>-10.55228843717313</v>
       </c>
       <c r="F58">
-        <v>-1.17131496827562</v>
+        <v>-1.987367861265108</v>
       </c>
       <c r="G58">
-        <v>0.4344748459056167</v>
+        <v>-0.9831735860121695</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.52338595084951</v>
       </c>
       <c r="E59">
-        <v>-8.01708113414098</v>
+        <v>-9.926734094701562</v>
       </c>
       <c r="F59">
-        <v>-1.62397053696359</v>
+        <v>-2.010982130816714</v>
       </c>
       <c r="G59">
-        <v>-0.1914003410212976</v>
+        <v>-0.979283695003526</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.784420851018188</v>
       </c>
       <c r="E60">
-        <v>-7.608721462025298</v>
+        <v>-10.54466701541822</v>
       </c>
       <c r="F60">
-        <v>-1.621441531282843</v>
+        <v>-2.172047403514841</v>
       </c>
       <c r="G60">
-        <v>-0.2503280516203247</v>
+        <v>-1.505839205206765</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.021145438006364</v>
       </c>
       <c r="E61">
-        <v>-7.209464022665033</v>
+        <v>-10.16477333091476</v>
       </c>
       <c r="F61">
-        <v>-1.545727093932163</v>
+        <v>-1.90695243890354</v>
       </c>
       <c r="G61">
-        <v>-0.8986619794856547</v>
+        <v>-2.00111668115497</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.219457862098762</v>
       </c>
       <c r="E62">
-        <v>-5.729590416276414</v>
+        <v>-9.352808884391445</v>
       </c>
       <c r="F62">
-        <v>-1.746702279729768</v>
+        <v>-2.104518064471223</v>
       </c>
       <c r="G62">
-        <v>-0.8795899266339134</v>
+        <v>-1.729443382565759</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.369361025453401</v>
       </c>
       <c r="E63">
-        <v>-6.400610637784992</v>
+        <v>-8.440253444735752</v>
       </c>
       <c r="F63">
-        <v>-1.623133885886763</v>
+        <v>-2.208472374950741</v>
       </c>
       <c r="G63">
-        <v>-0.8073670651491732</v>
+        <v>-1.437787631101507</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.465814218439925</v>
       </c>
       <c r="E64">
-        <v>-5.771727866917787</v>
+        <v>-9.014857926147021</v>
       </c>
       <c r="F64">
-        <v>-1.880504324466958</v>
+        <v>-2.127535081125409</v>
       </c>
       <c r="G64">
-        <v>-1.396015167486983</v>
+        <v>-2.069022591256501</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.503297498652314</v>
       </c>
       <c r="E65">
-        <v>-5.268378924017211</v>
+        <v>-8.408228076553508</v>
       </c>
       <c r="F65">
-        <v>-1.908228124703852</v>
+        <v>-2.182666245251328</v>
       </c>
       <c r="G65">
-        <v>-1.216550493803092</v>
+        <v>-2.21742441614541</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.489046086727555</v>
       </c>
       <c r="E66">
-        <v>-5.532656138630846</v>
+        <v>-7.402703065520343</v>
       </c>
       <c r="F66">
-        <v>-1.708441646129264</v>
+        <v>-2.171880073299476</v>
       </c>
       <c r="G66">
-        <v>-1.914999460041909</v>
+        <v>-1.974066213553586</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.422702402652827</v>
       </c>
       <c r="E67">
-        <v>-5.441973446627247</v>
+        <v>-8.417040486972434</v>
       </c>
       <c r="F67">
-        <v>-2.027203221298334</v>
+        <v>-2.225188000771832</v>
       </c>
       <c r="G67">
-        <v>-1.40638710666152</v>
+        <v>-2.311582952373362</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.320715659734811</v>
       </c>
       <c r="E68">
-        <v>-5.734046434699962</v>
+        <v>-8.384820394407859</v>
       </c>
       <c r="F68">
-        <v>-2.226799175370277</v>
+        <v>-2.319469465088861</v>
       </c>
       <c r="G68">
-        <v>-2.031481004841166</v>
+        <v>-2.513542782996601</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.188520991418097</v>
       </c>
       <c r="E69">
-        <v>-5.551349679334509</v>
+        <v>-8.043065517996993</v>
       </c>
       <c r="F69">
-        <v>-2.353338094719721</v>
+        <v>-2.405367851289558</v>
       </c>
       <c r="G69">
-        <v>-1.887111424419089</v>
+        <v>-2.61570290779297</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.043031353354265</v>
       </c>
       <c r="E70">
-        <v>-5.670928563981053</v>
+        <v>-8.28397127825704</v>
       </c>
       <c r="F70">
-        <v>-2.6792335699617</v>
+        <v>-2.780059136760844</v>
       </c>
       <c r="G70">
-        <v>-1.638966172977478</v>
+        <v>-3.08275136192781</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.892943054341545</v>
       </c>
       <c r="E71">
-        <v>-5.392001735952604</v>
+        <v>-8.271345892723655</v>
       </c>
       <c r="F71">
-        <v>-2.375706499697516</v>
+        <v>-2.637708340426764</v>
       </c>
       <c r="G71">
-        <v>-0.997034840185098</v>
+        <v>-2.640250602966666</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.747990386015121</v>
       </c>
       <c r="E72">
-        <v>-5.43605925957323</v>
+        <v>-7.92350474724648</v>
       </c>
       <c r="F72">
-        <v>-2.421781123008627</v>
+        <v>-2.83755363308695</v>
       </c>
       <c r="G72">
-        <v>-1.519227051367578</v>
+        <v>-2.897844151377357</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.614768188837092</v>
       </c>
       <c r="E73">
-        <v>-5.458982395000056</v>
+        <v>-8.400488914474399</v>
       </c>
       <c r="F73">
-        <v>-2.380298968578637</v>
+        <v>-2.484833964607517</v>
       </c>
       <c r="G73">
-        <v>-1.738156738425121</v>
+        <v>-2.57446013146473</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.490767337531258</v>
       </c>
       <c r="E74">
-        <v>-5.479922058811525</v>
+        <v>-8.578512284663937</v>
       </c>
       <c r="F74">
-        <v>-2.468292295941014</v>
+        <v>-2.777130857991948</v>
       </c>
       <c r="G74">
-        <v>-1.179412793943548</v>
+        <v>-2.63128564564632</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.378791605699649</v>
       </c>
       <c r="E75">
-        <v>-6.204668095947103</v>
+        <v>-8.402848249432395</v>
       </c>
       <c r="F75">
-        <v>-2.440770617350403</v>
+        <v>-2.813638666168128</v>
       </c>
       <c r="G75">
-        <v>-1.054774064935527</v>
+        <v>-2.373443806320183</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.26715271640989</v>
       </c>
       <c r="E76">
-        <v>-6.64569617955412</v>
+        <v>-9.612435356199201</v>
       </c>
       <c r="F76">
-        <v>-2.620767398672111</v>
+        <v>-2.732359256605441</v>
       </c>
       <c r="G76">
-        <v>-0.8463520494196307</v>
+        <v>-2.040118218153125</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.157551838017168</v>
       </c>
       <c r="E77">
-        <v>-6.593220222753236</v>
+        <v>-9.458684606690777</v>
       </c>
       <c r="F77">
-        <v>-2.697055894632931</v>
+        <v>-3.109504166323819</v>
       </c>
       <c r="G77">
-        <v>0.1272661514978683</v>
+        <v>-2.301942643763004</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.038767776111963</v>
       </c>
       <c r="E78">
-        <v>-7.596358727984359</v>
+        <v>-9.259540433729466</v>
       </c>
       <c r="F78">
-        <v>-2.780098898396179</v>
+        <v>-2.992705190896491</v>
       </c>
       <c r="G78">
-        <v>0.05996938177556364</v>
+        <v>-1.732965803019544</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.913480278745531</v>
       </c>
       <c r="E79">
-        <v>-7.838505290122508</v>
+        <v>-10.34396504739827</v>
       </c>
       <c r="F79">
-        <v>-2.653950968460856</v>
+        <v>-3.215787017572607</v>
       </c>
       <c r="G79">
-        <v>-0.2103465931425466</v>
+        <v>-1.760039444439703</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.778787805930691</v>
       </c>
       <c r="E80">
-        <v>-7.736777650014201</v>
+        <v>-11.46127091083677</v>
       </c>
       <c r="F80">
-        <v>-3.047441223771274</v>
+        <v>-3.540550114574958</v>
       </c>
       <c r="G80">
-        <v>-0.1452016780207682</v>
+        <v>-1.866831022445513</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.638706872725241</v>
       </c>
       <c r="E81">
-        <v>-9.576008311281502</v>
+        <v>-11.73716818975409</v>
       </c>
       <c r="F81">
-        <v>-3.154299790365008</v>
+        <v>-3.507183475590195</v>
       </c>
       <c r="G81">
-        <v>-0.05432058187669555</v>
+        <v>-1.441147834823867</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.499393517259314</v>
       </c>
       <c r="E82">
-        <v>-10.43454358449969</v>
+        <v>-12.53785220752429</v>
       </c>
       <c r="F82">
-        <v>-3.268095933957187</v>
+        <v>-3.051761159776874</v>
       </c>
       <c r="G82">
-        <v>0.8291978116439989</v>
+        <v>-1.67983816820532</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.364493673650859</v>
       </c>
       <c r="E83">
-        <v>-10.53925548897906</v>
+        <v>-13.23361601101078</v>
       </c>
       <c r="F83">
-        <v>-3.445094853648163</v>
+        <v>-3.604457002966135</v>
       </c>
       <c r="G83">
-        <v>0.3665126565299185</v>
+        <v>-0.9619728523786769</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.244558689290887</v>
       </c>
       <c r="E84">
-        <v>-11.82737992046089</v>
+        <v>-14.15359361956504</v>
       </c>
       <c r="F84">
-        <v>-3.471102276626457</v>
+        <v>-3.875794544324933</v>
       </c>
       <c r="G84">
-        <v>1.404179981995697</v>
+        <v>-0.8736375657543038</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.138517768133577</v>
       </c>
       <c r="E85">
-        <v>-12.61088290784599</v>
+        <v>-15.23864769112092</v>
       </c>
       <c r="F85">
-        <v>-3.962636440997419</v>
+        <v>-3.749662353370263</v>
       </c>
       <c r="G85">
-        <v>0.7442293498330645</v>
+        <v>-1.51808160261099</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.055692361616344</v>
       </c>
       <c r="E86">
-        <v>-14.28368309238339</v>
+        <v>-16.60765972532776</v>
       </c>
       <c r="F86">
-        <v>-3.92366423979791</v>
+        <v>-3.833915601909001</v>
       </c>
       <c r="G86">
-        <v>1.065875333337575</v>
+        <v>-0.4891044591857984</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.990822624873045</v>
       </c>
       <c r="E87">
-        <v>-15.29116893266188</v>
+        <v>-17.33162686493402</v>
       </c>
       <c r="F87">
-        <v>-4.174323245680624</v>
+        <v>-3.807695288508188</v>
       </c>
       <c r="G87">
-        <v>1.830472309996569</v>
+        <v>-1.012965185320071</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.947741033263405</v>
       </c>
       <c r="E88">
-        <v>-16.05409000568212</v>
+        <v>-19.22305271761373</v>
       </c>
       <c r="F88">
-        <v>-4.119066998076883</v>
+        <v>-4.039941343761474</v>
       </c>
       <c r="G88">
-        <v>1.34875151803168</v>
+        <v>-0.7248550281283781</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.920596571559836</v>
       </c>
       <c r="E89">
-        <v>-18.60113473977032</v>
+        <v>-20.31884380104178</v>
       </c>
       <c r="F89">
-        <v>-4.180937759391978</v>
+        <v>-4.186691599371824</v>
       </c>
       <c r="G89">
-        <v>1.605206238776862</v>
+        <v>-0.451268234217468</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.90613446798866</v>
       </c>
       <c r="E90">
-        <v>-19.26668003620362</v>
+        <v>-22.50280454614299</v>
       </c>
       <c r="F90">
-        <v>-4.312344993967675</v>
+        <v>-4.360901406017573</v>
       </c>
       <c r="G90">
-        <v>1.498815236781303</v>
+        <v>-0.4646593909238199</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.899207665669565</v>
       </c>
       <c r="E91">
-        <v>-22.03922013350377</v>
+        <v>-24.12606775351048</v>
       </c>
       <c r="F91">
-        <v>-4.598990764930208</v>
+        <v>-4.653915665572828</v>
       </c>
       <c r="G91">
-        <v>0.7168842436786845</v>
+        <v>-1.068003004910455</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.892368448531215</v>
       </c>
       <c r="E92">
-        <v>-22.88217745613557</v>
+        <v>-25.98228924925456</v>
       </c>
       <c r="F92">
-        <v>-5.025001896107131</v>
+        <v>-4.91337690347769</v>
       </c>
       <c r="G92">
-        <v>1.312371933100628</v>
+        <v>-1.042796511174444</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.886854831354592</v>
       </c>
       <c r="E93">
-        <v>-25.21985725142715</v>
+        <v>-26.88693344481885</v>
       </c>
       <c r="F93">
-        <v>-4.831218596100632</v>
+        <v>-5.004384659818855</v>
       </c>
       <c r="G93">
-        <v>0.6263044071786856</v>
+        <v>-1.437582377278072</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.877995249046032</v>
       </c>
       <c r="E94">
-        <v>-27.47600640068463</v>
+        <v>-29.74513415644809</v>
       </c>
       <c r="F94">
-        <v>-4.911083154139338</v>
+        <v>-5.022603772476027</v>
       </c>
       <c r="G94">
-        <v>0.235103861894088</v>
+        <v>-1.242912367932308</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.875559398291029</v>
       </c>
       <c r="E95">
-        <v>-29.51706888423679</v>
+        <v>-32.42294084174478</v>
       </c>
       <c r="F95">
-        <v>-5.333250660567272</v>
+        <v>-5.13085896651088</v>
       </c>
       <c r="G95">
-        <v>-0.8295940678998399</v>
+        <v>-1.744536159679297</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.883669200245041</v>
       </c>
       <c r="E96">
-        <v>-32.79368474451574</v>
+        <v>-34.11101783334706</v>
       </c>
       <c r="F96">
-        <v>-5.265403228440979</v>
+        <v>-5.103618932837222</v>
       </c>
       <c r="G96">
-        <v>-0.9221569211778623</v>
+        <v>-2.346962752551553</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.911437545735473</v>
       </c>
       <c r="E97">
-        <v>-35.23607870852369</v>
+        <v>-36.46672095518916</v>
       </c>
       <c r="F97">
-        <v>-5.479439283078523</v>
+        <v>-5.569087688511694</v>
       </c>
       <c r="G97">
-        <v>-1.021940074277035</v>
+        <v>-2.098711563652685</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.973798876941259</v>
       </c>
       <c r="E98">
-        <v>-36.91152352188157</v>
+        <v>-39.04962214647009</v>
       </c>
       <c r="F98">
-        <v>-5.490015878077467</v>
+        <v>-5.478695409150809</v>
       </c>
       <c r="G98">
-        <v>-1.564200812518577</v>
+        <v>-2.706511171935179</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.068921901669188</v>
       </c>
       <c r="E99">
-        <v>-40.09547095430456</v>
+        <v>-41.47772424650982</v>
       </c>
       <c r="F99">
-        <v>-5.725689717643538</v>
+        <v>-5.842840749217055</v>
       </c>
       <c r="G99">
-        <v>-2.255638043305218</v>
+        <v>-3.402152795556694</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.226493799144428</v>
       </c>
       <c r="E100">
-        <v>-42.08858821930051</v>
+        <v>-43.75079856737097</v>
       </c>
       <c r="F100">
-        <v>-5.792094133754155</v>
+        <v>-5.728975022763041</v>
       </c>
       <c r="G100">
-        <v>-2.673405716542467</v>
+        <v>-3.735657153182873</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.419083895675371</v>
       </c>
       <c r="E101">
-        <v>-44.85583226624868</v>
+        <v>-46.72361269189734</v>
       </c>
       <c r="F101">
-        <v>-6.002170592206318</v>
+        <v>-5.724325396531127</v>
       </c>
       <c r="G101">
-        <v>-3.472177454803358</v>
+        <v>-4.244176811288163</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.711922830434984</v>
       </c>
       <c r="E102">
-        <v>-47.17413019278743</v>
+        <v>-48.70669259425529</v>
       </c>
       <c r="F102">
-        <v>-6.104869926070595</v>
+        <v>-6.265733077122439</v>
       </c>
       <c r="G102">
-        <v>-3.22910726967345</v>
+        <v>-4.333690652124517</v>
       </c>
     </row>
   </sheetData>
